--- a/astro-site/public/dl/pizza-shop-checklist-templates/07-blank-pizza-shop-checklist-template.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/07-blank-pizza-shop-checklist-template.xlsx
@@ -1673,7 +1673,7 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BAR — type your bar tasks below</t>
+          <t xml:space="preserve">  COUNTER / BAR — type your counter or bar tasks below</t>
         </is>
       </c>
       <c r="B19" s="26" t="n"/>
@@ -1690,7 +1690,7 @@
       <c r="B20" s="29" t="n"/>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Counter / bar</t>
         </is>
       </c>
       <c r="D20" s="31" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="B21" s="29" t="inlineStr"/>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Counter / bar</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       <c r="B22" s="29" t="inlineStr"/>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Counter / bar</t>
         </is>
       </c>
       <c r="D22" s="31" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
       <c r="B23" s="29" t="inlineStr"/>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Counter / bar</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
       <c r="B24" s="29" t="inlineStr"/>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Counter / bar</t>
         </is>
       </c>
       <c r="D24" s="31" t="inlineStr"/>
